--- a/VoAnhKiet_1150080143.xlsx
+++ b/VoAnhKiet_1150080143.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Software-Testing\Buoi3\1150080143_VoAnhKiet_CNPM2_Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E032C6F-DA99-4EB8-BEBE-0B000393C84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA587C5A-7442-4DEC-9C23-B496A206DBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="442">
   <si>
     <t>1. Phạm vi đầu vào</t>
   </si>
@@ -1129,15 +1129,6 @@
     <t>Do có 2 điều kiện đầu vào</t>
   </si>
   <si>
-    <t>Tổng số rules = $2^2 = 4$ rules.</t>
-  </si>
-  <si>
-    <t>Tuổi $\ge$ 21</t>
-  </si>
-  <si>
-    <t>Số tiền gửi $\ge$ 100</t>
-  </si>
-  <si>
     <t>Tuổi &gt;= 21</t>
   </si>
   <si>
@@ -1163,6 +1154,213 @@
   </si>
   <si>
     <t>Biến Số tiền (Mốc quan trọng: 100)</t>
+  </si>
+  <si>
+    <t>BÀI BONUS – KIỂM THỬ HỆ THỐNG QUÉT THẺ ĂN TRƯA</t>
+  </si>
+  <si>
+    <t>Các biến trạng thái</t>
+  </si>
+  <si>
+    <t>4. Lịch sử ăn (Đã ăn/Chưa ăn)</t>
+  </si>
+  <si>
+    <t>Biến giới hạn số học</t>
+  </si>
+  <si>
+    <t>Vùng Hợp lệ (Cho phép ăn)</t>
+  </si>
+  <si>
+    <t>- Đã đăng ký trước + Trong giờ + Chưa ăn.</t>
+  </si>
+  <si>
+    <t>Vùng Không hợp lệ (Từ chối)</t>
+  </si>
+  <si>
+    <t>- Mã cán bộ sai/rỗng.</t>
+  </si>
+  <si>
+    <t>- Ngoài giờ phục vụ.</t>
+  </si>
+  <si>
+    <t>- Đã ăn rồi (Quẹt thẻ lần 2).</t>
+  </si>
+  <si>
+    <t>Giá trị (Thứ tự người đến thêm)</t>
+  </si>
+  <si>
+    <t>Invalid (Không tồn tại)</t>
+  </si>
+  <si>
+    <t>1 (Người đầu tiên)</t>
+  </si>
+  <si>
+    <t>Valid (Được ăn - Tính vào 10%)</t>
+  </si>
+  <si>
+    <t>10 (Người thứ 10)</t>
+  </si>
+  <si>
+    <t>Valid (Được ăn - Đạt giới hạn biên)</t>
+  </si>
+  <si>
+    <t>11 (Người thứ 11)</t>
+  </si>
+  <si>
+    <t>Invalid (Từ chối - Hết suất dự phòng)</t>
+  </si>
+  <si>
+    <t>Dữ liệu nhập / Trạng thái</t>
+  </si>
+  <si>
+    <t>Mã cán bộ không tồn tại</t>
+  </si>
+  <si>
+    <t>Mã: "INVALID"</t>
+  </si>
+  <si>
+    <t>Báo lỗi / Từ chối</t>
+  </si>
+  <si>
+    <t>Đã đăng ký, đi đúng giờ, chưa ăn</t>
+  </si>
+  <si>
+    <t>Chấp nhận (OK)</t>
+  </si>
+  <si>
+    <t>Mã: Hợp lệĐK: CóGiờ: TrongĐã ăn: Không</t>
+  </si>
+  <si>
+    <t>Đã đăng ký, đi sai giờ</t>
+  </si>
+  <si>
+    <t>Mã: Hợp lệĐK: CóGiờ: Ngoài</t>
+  </si>
+  <si>
+    <t>Từ chối (Hết giờ)</t>
+  </si>
+  <si>
+    <t>Đã đăng ký, nhưng đã ăn rồi</t>
+  </si>
+  <si>
+    <t>Mã: Hợp lệĐK: CóĐã ăn: Có</t>
+  </si>
+  <si>
+    <t>Từ chối (Đã dùng bữa)</t>
+  </si>
+  <si>
+    <t>Chưa đăng ký, còn suất dự phòng (Biên dưới)</t>
+  </si>
+  <si>
+    <t>Mã: Hợp lệĐK: KhôngBộ đếm 10%: 1</t>
+  </si>
+  <si>
+    <t>Chấp nhận (Diện vãng lai)</t>
+  </si>
+  <si>
+    <t>Chưa đăng ký, còn suất dự phòng (Tại biên Max)</t>
+  </si>
+  <si>
+    <t>Mã: Hợp lệĐK: KhôngBộ đếm 10%: 10</t>
+  </si>
+  <si>
+    <t>Chưa đăng ký, hết suất dự phòng (Vượt biên)</t>
+  </si>
+  <si>
+    <t>Mã: Hợp lệĐK: KhôngBộ đếm 10%: 11</t>
+  </si>
+  <si>
+    <t>Từ chối (Hết suất dự phòng)</t>
+  </si>
+  <si>
+    <t>Cán bộ thuộc diện "Ngừng hỗ trợ"</t>
+  </si>
+  <si>
+    <t>Mã: Hợp lệTT Hỗ trợ: Ngừng</t>
+  </si>
+  <si>
+    <t>Từ chối / Thu tiền toàn bộ</t>
+  </si>
+  <si>
+    <t>Các điều kiện: Trong giờ phục vụ, đã dùng cơm, đã đăng ký, thuộc diện 10% người chưa đăng ký</t>
+  </si>
+  <si>
+    <t>Hành động: Chấp nhận, từ chối</t>
+  </si>
+  <si>
+    <t>Tổng số rules = 2^2 = 4 rules.</t>
+  </si>
+  <si>
+    <t>Trong giờ phục vụ</t>
+  </si>
+  <si>
+    <t>Đã dùng cơm</t>
+  </si>
+  <si>
+    <t>Đã đăng ký</t>
+  </si>
+  <si>
+    <t>Thuộc diện 10%</t>
+  </si>
+  <si>
+    <t>Chấp nhận</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>Nhóm 1 (Sai giờ): Nếu "Trong giờ phục vụ" là False, hệ thống luôn Từ chối bất kể các điều kiện khác. Gộp R9 đến R16 thành 1 rule.</t>
+  </si>
+  <si>
+    <t>Nhóm 2 (Đã ăn rồi): Nếu "Trong giờ" (T) nhưng "Đã dùng cơm" là True, hệ thống luôn Từ chối. Gộp R1 đến R4 thành 1 rule.</t>
+  </si>
+  <si>
+    <t>Nhóm 3 (Đã đăng ký): Nếu "Trong giờ" (T), "Đã dùng cơm" (F) và "Đã đăng ký" (T) thì luôn được Chấp nhận (điều kiện 10% không quan trọng với người đã đăng ký). Gộp R5, R6 thành 1 rule.</t>
+  </si>
+  <si>
+    <t>Nhóm 4 (Khách vãng lai hợp lệ): Nếu "Trong giờ" (T), "Đã dùng cơm" (F), "Đã đăng ký" (F) nhưng "Thuộc diện 10%" (T). Giữ nguyên R7.</t>
+  </si>
+  <si>
+    <t>Nhóm 5 (Khách vãng lai quá tải): Nếu "Trong giờ" (T), "Đã dùng cơm" (F), "Đã đăng ký" (F) và "Thuộc diện 10%" (F). Giữ nguyên R8.</t>
+  </si>
+  <si>
+    <t>TC1: Quẹt thẻ ngoài giờ phục vụ (sớm hoặc muộn): Hệ thống báo lỗi/Từ chối.</t>
+  </si>
+  <si>
+    <t>TC2: Quẹt thẻ trong giờ, nhưng hệ thống ghi nhận đã ăn suất hôm nay rồi: Từ chối.</t>
+  </si>
+  <si>
+    <t>TC3: Cán bộ đã đăng ký, đi đúng giờ, chưa ăn: Chấp nhận (Mời vào).</t>
+  </si>
+  <si>
+    <t>TC4: Cán bộ chưa đăng ký, đi đúng giờ, chưa ăn, nhà ăn vẫn còn suất dự phòng (trong 10%): Chấp nhận (Diện vãng lai).</t>
+  </si>
+  <si>
+    <t>TC5: Cán bộ chưa đăng ký, đi đúng giờ, chưa ăn, nhưng nhà ăn đã quá tải (hết 10% dự phòng): Từ chối.</t>
+  </si>
+  <si>
+    <t>Bộ đếm khách vãng lai: Cho phép thêm 10% so với tổng đăng ký.</t>
+  </si>
+  <si>
+    <t>- Chưa đăng ký + Trong giờ + Chưa ăn + Nằm trong 10% cho phép.</t>
+  </si>
+  <si>
+    <t>- Chưa đăng ký + Vượt quá 10% cho phép.</t>
+  </si>
+  <si>
+    <t>Mã cán bộ</t>
+  </si>
+  <si>
+    <t>3. Trạng thái đặt cơm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Trạng thái hỗ trợ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Thời gian </t>
+  </si>
+  <si>
+    <t>Bước 3: Lập Bảng quyết định kiểm tra hệ thống quét thẻ ăn trưa</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1388,7 @@
       <family val="1"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
@@ -1205,7 +1403,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1228,11 +1426,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1274,15 +1485,27 @@
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1291,6 +1514,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1569,7 +1797,7 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" style="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.5546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="38.44140625" style="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="1"/>
@@ -1586,36 +1814,36 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="21" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1625,26 +1853,26 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2342,56 +2570,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="21" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -2400,42 +2628,42 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
@@ -2526,11 +2754,11 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
@@ -3136,11 +3364,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED72998-3205-46E1-B325-11A7E112045F}">
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" style="12" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" style="12" customWidth="1"/>
     <col min="3" max="3" width="31.109375" style="12" customWidth="1"/>
     <col min="4" max="4" width="38.44140625" style="12" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="12"/>
@@ -3157,273 +3385,283 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="16" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13" t="s">
         <v>149</v>
       </c>
     </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>5</v>
+      <c r="A9" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="s">
+      <c r="A10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>10</v>
+      <c r="C15" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>7</v>
+        <v>13</v>
+      </c>
+      <c r="B16" s="10">
+        <v>0</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>75</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="10">
-        <v>6</v>
-      </c>
-      <c r="C23" s="10" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>21</v>
+      <c r="A26" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>24</v>
+        <v>80</v>
+      </c>
+      <c r="C27" s="10">
+        <v>0</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" s="10">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>60</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
+      </c>
+      <c r="C33" s="10">
+        <v>6</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>162</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C34" s="10">
-        <v>6</v>
+        <v>35</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>36</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>27</v>
@@ -3431,154 +3669,169 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>27</v>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="12" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="12" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="12" t="s">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="12" t="s">
         <v>296</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>54</v>
@@ -3587,16 +3840,16 @@
         <v>54</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>55</v>
@@ -3607,16 +3860,16 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>55</v>
@@ -3625,10 +3878,10 @@
         <v>54</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I63" s="10" t="s">
         <v>55</v>
@@ -3636,171 +3889,159 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E64" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="H64" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="I64" s="10" t="s">
-        <v>55</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10"/>
+      <c r="I64" s="10"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B65" s="10"/>
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
       <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
+      <c r="F65" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
       <c r="I65" s="10"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
       <c r="E66" s="10"/>
-      <c r="F66" s="10" t="s">
-        <v>59</v>
-      </c>
+      <c r="F66" s="10"/>
       <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
+      <c r="H66" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="I66" s="10"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
+        <v>61</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="F67" s="10"/>
       <c r="G67" s="10"/>
-      <c r="H67" s="10" t="s">
-        <v>59</v>
-      </c>
+      <c r="H67" s="10"/>
       <c r="I67" s="10"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B68" s="10"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
       <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
+      <c r="G68" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="H68" s="10"/>
       <c r="I68" s="10"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="B69" s="10"/>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
       <c r="F69" s="10"/>
-      <c r="G69" s="10" t="s">
-        <v>59</v>
-      </c>
+      <c r="G69" s="10"/>
       <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70" s="10"/>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10" t="s">
-        <v>59</v>
+      <c r="I69" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="12" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="12" t="s">
         <v>170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>55</v>
@@ -3808,7 +4049,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>114</v>
@@ -3817,90 +4058,80 @@
         <v>54</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>54</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
+      <c r="C80" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="D80" s="10"/>
       <c r="E80" s="10"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B81" s="10"/>
-      <c r="C81" s="10" t="s">
-        <v>59</v>
-      </c>
+      <c r="C81" s="10"/>
       <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
+      <c r="E81" s="10" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B82" s="10"/>
+        <v>61</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
-      <c r="E82" s="10" t="s">
-        <v>59</v>
-      </c>
+      <c r="E82" s="10"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B83" s="10" t="s">
-        <v>59</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B83" s="10"/>
       <c r="C83" s="10"/>
-      <c r="D83" s="10"/>
+      <c r="D83" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="E83" s="10"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
-      <c r="D84" s="10" t="s">
-        <v>59</v>
-      </c>
+      <c r="D84" s="10"/>
       <c r="E84" s="10"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="2"/>
@@ -3909,54 +4140,44 @@
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="12" t="s">
         <v>175</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:A7"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA7786D-17A8-439B-A2EF-812007703391}">
-  <dimension ref="A1:Q108"/>
+  <dimension ref="A1:Q107"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" style="1" customWidth="1"/>
@@ -3977,125 +4198,132 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="17"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="7" t="s">
         <v>181</v>
       </c>
     </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
+      <c r="A10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>182</v>
+      <c r="A11" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>184</v>
+      <c r="A12" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>186</v>
+      <c r="A13" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B14" s="7" t="s">
         <v>189</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>10</v>
+      <c r="A17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>190</v>
+        <v>13</v>
+      </c>
+      <c r="B18" s="7">
+        <v>-1</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B19" s="7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="B20" s="7">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>191</v>
@@ -4103,120 +4331,123 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B21" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B22" s="7">
-        <v>100</v>
+        <v>499</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B23" s="7">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B24" s="7">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B25" s="7">
-        <v>501</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>21</v>
+      <c r="A29" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="C30" s="8">
+        <v>-1</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="8">
-        <v>-1</v>
+        <v>202</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>206</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>205</v>
@@ -4224,255 +4455,294 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>203</v>
+        <v>213</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>205</v>
+        <v>218</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>40</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
         <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
         <v>224</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>226</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>101</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>228</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>105</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>229</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A66" s="1" t="s">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A67" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="M67" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="N67" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="O67" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="P67" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q67" s="7" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="s">
-        <v>45</v>
+        <v>237</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>308</v>
+        <v>55</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>309</v>
+        <v>55</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>310</v>
+        <v>55</v>
       </c>
       <c r="M68" s="7" t="s">
-        <v>311</v>
+        <v>55</v>
       </c>
       <c r="N68" s="7" t="s">
-        <v>312</v>
+        <v>55</v>
       </c>
       <c r="O68" s="7" t="s">
-        <v>313</v>
+        <v>55</v>
       </c>
       <c r="P68" s="7" t="s">
-        <v>314</v>
+        <v>55</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>315</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>54</v>
@@ -4481,10 +4751,10 @@
         <v>54</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>54</v>
@@ -4493,16 +4763,16 @@
         <v>54</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K69" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L69" s="7" t="s">
         <v>55</v>
@@ -4511,10 +4781,10 @@
         <v>55</v>
       </c>
       <c r="N69" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P69" s="7" t="s">
         <v>55</v>
@@ -4525,7 +4795,7 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>54</v>
@@ -4534,16 +4804,16 @@
         <v>54</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>55</v>
@@ -4558,16 +4828,16 @@
         <v>54</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M70" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O70" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P70" s="7" t="s">
         <v>55</v>
@@ -4578,28 +4848,28 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>54</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>55</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>55</v>
@@ -4608,22 +4878,22 @@
         <v>54</v>
       </c>
       <c r="K71" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L71" s="7" t="s">
         <v>54</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N71" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O71" s="7" t="s">
         <v>55</v>
       </c>
       <c r="P71" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q71" s="7" t="s">
         <v>55</v>
@@ -4631,70 +4901,56 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I72" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K72" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M72" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O72" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="P72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q72" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="7"/>
+      <c r="H72" s="7"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
+      <c r="M72" s="7"/>
+      <c r="N72" s="7"/>
+      <c r="O72" s="7"/>
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
+        <v>234</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
@@ -4705,46 +4961,32 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J74" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K74" s="7"/>
+        <v>235</v>
+      </c>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
       <c r="N74" s="7"/>
       <c r="O74" s="7"/>
-      <c r="P74" s="7"/>
+      <c r="P74" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="Q74" s="7"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -4755,148 +4997,146 @@
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7"/>
-      <c r="K75" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
-      <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
-      <c r="P75" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M75" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N75" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O75" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M76" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="N76" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="O76" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A80" s="1" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="1" t="s">
         <v>241</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
         <v>247</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="s">
-        <v>45</v>
+        <v>230</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>248</v>
+        <v>55</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>55</v>
@@ -4907,7 +5147,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>114</v>
@@ -4919,18 +5159,18 @@
         <v>54</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>114</v>
@@ -4939,47 +5179,39 @@
         <v>54</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>114</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B97" s="7"/>
-      <c r="C97" s="7"/>
+        <v>234</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
       <c r="F97" s="7"/>
@@ -4987,87 +5219,72 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D98" s="7"/>
+        <v>235</v>
+      </c>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E98" s="7"/>
-      <c r="F98" s="7"/>
+      <c r="F98" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="G98" s="7"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
-      <c r="D99" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G99" s="7"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="B100" s="7"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F100" s="7"/>
-      <c r="G100" s="7" t="s">
-        <v>59</v>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F99" s="7"/>
+      <c r="G99" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>68</v>
+        <v>250</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="1" t="s">
         <v>254</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5079,7 +5296,7 @@
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" style="12" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="44" style="12" customWidth="1"/>
     <col min="3" max="3" width="31.109375" style="12" customWidth="1"/>
     <col min="4" max="4" width="38.44140625" style="12" customWidth="1"/>
     <col min="5" max="5" width="24.5546875" style="12" customWidth="1"/>
@@ -5097,34 +5314,34 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="7" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5142,42 +5359,42 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="7" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="7" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="7" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="7" t="s">
         <v>268</v>
       </c>
     </row>
@@ -5904,7 +6121,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2017C8-1E22-4586-A9CD-7B97D8DEBEA1}">
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28" style="12" customWidth="1"/>
@@ -5925,42 +6142,42 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="7" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C7" s="3"/>
+      <c r="B7" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C8" s="3"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C8" s="14"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
@@ -5968,549 +6185,541 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="7" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="2" t="s">
-        <v>331</v>
+      <c r="A14" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="17"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="7" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="2" t="s">
-        <v>344</v>
+      <c r="A17" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>10</v>
+      <c r="A19" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C19" s="7">
+        <v>20</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>7</v>
+        <v>339</v>
+      </c>
+      <c r="C20" s="7">
+        <v>21</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>12</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>337</v>
       </c>
       <c r="C21" s="7">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>339</v>
       </c>
       <c r="C22" s="7">
+        <v>100</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C23" s="7">
-        <v>99</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="C24" s="7">
-        <v>100</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>343</v>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
-        <v>21</v>
+      <c r="A27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>23</v>
+        <v>348</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>24</v>
+        <v>349</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>25</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="C34" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D32" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="12" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="12" t="s">
         <v>109</v>
       </c>
     </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="12" t="s">
+        <v>328</v>
+      </c>
+    </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="12" t="s">
-        <v>328</v>
+      <c r="A54" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
-        <v>45</v>
+        <v>365</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
-        <v>57</v>
+        <v>353</v>
       </c>
       <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
+      <c r="C59" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="B60" s="7"/>
       <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
+      <c r="D60" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E60" s="7"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B61" s="7"/>
-      <c r="C61" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="C61" s="7"/>
       <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E62" s="7"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="12" t="s">
+      <c r="E61" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="12" t="s">
         <v>63</v>
       </c>
     </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="12" t="s">
+        <v>366</v>
+      </c>
+    </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="12" t="s">
-        <v>369</v>
+      <c r="A67" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
-        <v>45</v>
+        <v>365</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="A70" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>55</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
-        <v>57</v>
+        <v>353</v>
       </c>
       <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
+      <c r="C72" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="B73" s="7"/>
       <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
+      <c r="D73" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="E73" s="7"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B74" s="7"/>
-      <c r="C74" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="C74" s="7"/>
       <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E75" s="7"/>
+      <c r="E74" s="7" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7" t="s">
-        <v>59</v>
+      <c r="A76" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="12" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
-        <v>68</v>
+        <v>368</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="12" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="12" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="C7:C8"/>
@@ -6521,9 +6730,1042 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228E6332-0A6F-497D-AE63-5A9DE9A86712}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:Q102"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28" style="12" customWidth="1"/>
+    <col min="2" max="2" width="72.5546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="38.44140625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="15" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
+      <c r="B8" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="17"/>
+      <c r="B9" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>434</v>
+      </c>
+      <c r="C10" s="18"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="21"/>
+      <c r="B16" s="7" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="21"/>
+      <c r="B18" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="21"/>
+      <c r="B19" s="7" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="21"/>
+      <c r="B20" s="7" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="10">
+        <v>-1</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="10">
+        <v>5</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28" s="10">
+        <v>9</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="12" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A67" s="12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A69" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J69" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K69" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="O69" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q69" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A70" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J70" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="O70" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P70" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q70" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A71" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q71" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A72" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O72" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q72" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A73" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q73" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A74" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
+      <c r="H74" s="10"/>
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="10"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="10"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A75" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B75" s="10"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A76" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F76" s="10"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="M76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="O76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="P76" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q76" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A79" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A80" s="12" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="12" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="12" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B92" s="10"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B93" s="10"/>
+      <c r="C93" s="10"/>
+      <c r="D93" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F93" s="10"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" s="12" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" s="12" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" s="12" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" s="12" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" s="12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A17:A20"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/VoAnhKiet_1150080143.xlsx
+++ b/VoAnhKiet_1150080143.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Software-Testing\Buoi5\1150080143_VoAnhKiet_CNPM2_Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A432E9-EDD5-405B-B75D-BFECB405E8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC65DB8-4567-40AF-ADCD-F333676E466E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="219">
   <si>
     <t>Võ Anh Kiệt</t>
   </si>
@@ -135,9 +135,6 @@
     <t>.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pass </t>
-  </si>
-  <si>
     <t>TC_07</t>
   </si>
   <si>
@@ -934,48 +931,30 @@
     <t>Tuổi: 10Giới tính: Nam/Nữ</t>
   </si>
   <si>
-    <t>1. Gọi HealthCheckUtils.calculateFee(10, "Nam").2. So sánh kết quả.</t>
-  </si>
-  <si>
     <t>Kiểm tra phí Nam thanh niên (testMaleYoung)</t>
   </si>
   <si>
     <t>Tuổi: 25Giới tính: Nam</t>
   </si>
   <si>
-    <t>1. Gọi HealthCheckUtils.calculateFee(25, "Nam").2. So sánh kết quả.</t>
-  </si>
-  <si>
     <t>Kiểm tra phí Nữ thanh niên (testFemaleYoung)</t>
   </si>
   <si>
     <t>Tuổi: 25Giới tính: Nữ</t>
   </si>
   <si>
-    <t>1. Gọi HealthCheckUtils.calculateFee(25, "Nữ").2. So sánh kết quả.</t>
-  </si>
-  <si>
     <t>Kiểm tra phí Người cao tuổi (testSeniorFee)</t>
   </si>
   <si>
     <t>Tuổi: 60Giới tính: Nữ</t>
   </si>
   <si>
-    <t>1. Gọi HealthCheckUtils.calculateFee(60, "Nữ").2. So sánh kết quả.</t>
-  </si>
-  <si>
     <t>Kiểm tra ngoại lệ tuổi âm (testInvalidAge)</t>
   </si>
   <si>
     <t>Tuổi: -5Giới tính: Nam</t>
   </si>
   <si>
-    <t>1. Gọi HealthCheckUtils.calculateFee(-5, "Nam").2. Bắt ngoại lệ trả về.</t>
-  </si>
-  <si>
-    <t>Ném ra IllegalArgumentException ("Tuổi không hợp lệ")</t>
-  </si>
-  <si>
     <t>1. Trẻ em (0 - 17 tuổi): Phí cố định 50 Euro (Không phân biệt giới tính).</t>
   </si>
   <si>
@@ -1059,9 +1038,6 @@
     <t>Thành công</t>
   </si>
   <si>
-    <t>Lỗi Mã KH để trống (testIdEmpty)</t>
-  </si>
-  <si>
     <t>Mã KH: ""</t>
   </si>
   <si>
@@ -1074,9 +1050,6 @@
     <t>Đúng thông báo</t>
   </si>
   <si>
-    <t>Lỗi Mã KH quá ngắn (testIdTooShort)</t>
-  </si>
-  <si>
     <t>Mã KH: "ABC12"</t>
   </si>
   <si>
@@ -1086,9 +1059,6 @@
     <t>Lỗi: "Mã Khách Hàng phải từ 6 đến 10 ký tự."</t>
   </si>
   <si>
-    <t>Lỗi Mã KH chứa ký tự đặc biệt (testIdSpecial)</t>
-  </si>
-  <si>
     <t>Mã KH: "User@123"</t>
   </si>
   <si>
@@ -1098,9 +1068,6 @@
     <t>Lỗi: "Mã Khách Hàng chỉ được chứa chữ cái và số."</t>
   </si>
   <si>
-    <t>Lỗi Trùng Mã KH (testIdDuplicate)</t>
-  </si>
-  <si>
     <t>Mã KH: "EXIST01"</t>
   </si>
   <si>
@@ -1110,9 +1077,6 @@
     <t>Lỗi: "Mã Khách Hàng đã tồn tại..."</t>
   </si>
   <si>
-    <t>Lỗi Email sai định dạng (testEmailInvalid)</t>
-  </si>
-  <si>
     <t>Email: "abc.com"</t>
   </si>
   <si>
@@ -1122,9 +1086,6 @@
     <t>Lỗi: "Vui lòng nhập đúng định dạng email..."</t>
   </si>
   <si>
-    <t>Lỗi SĐT không bắt đầu bằng 0 (testPhoneNoZero)</t>
-  </si>
-  <si>
     <t>SĐT: "9123456789"</t>
   </si>
   <si>
@@ -1134,9 +1095,6 @@
     <t>Lỗi: "Số điện thoại phải bắt đầu bằng số 0."</t>
   </si>
   <si>
-    <t>Lỗi SĐT chứa chữ cái (testPhoneLetters)</t>
-  </si>
-  <si>
     <t>SĐT: "098abc"</t>
   </si>
   <si>
@@ -1146,9 +1104,6 @@
     <t>Lỗi: "Số điện thoại chỉ được phép nhập số."</t>
   </si>
   <si>
-    <t>Lỗi chưa đủ 18 tuổi (testUnderAge)</t>
-  </si>
-  <si>
     <t>NS: 01/01/2010</t>
   </si>
   <si>
@@ -1158,9 +1113,6 @@
     <t>Lỗi: "Bạn phải đủ 18 tuổi để đăng ký."</t>
   </si>
   <si>
-    <t>Lỗi chưa đồng ý điều khoản (testTosNotAgreed)</t>
-  </si>
-  <si>
     <t>TOS: False</t>
   </si>
   <si>
@@ -1183,6 +1135,51 @@
   </si>
   <si>
     <t>5. Điều khoản: Bắt buộc phải tích chọn đồng ý.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>1. Gọi calculateFee(10, "Nam").2. So sánh kết quả.</t>
+  </si>
+  <si>
+    <t>1. Gọi calculateFee(25, "Nam").2. So sánh kết quả.</t>
+  </si>
+  <si>
+    <t>1. Gọi calculateFee(25, "Nữ").2. So sánh kết quả.</t>
+  </si>
+  <si>
+    <t>1. Gọi calculateFee(60, "Nữ").2. So sánh kết quả.</t>
+  </si>
+  <si>
+    <t>1. Gọi calculateFee(-5, "Nam").2. Bắt ngoại lệ trả về.</t>
+  </si>
+  <si>
+    <t>Lỗi Mã KH để trống</t>
+  </si>
+  <si>
+    <t>Lỗi Mã KH quá ngắn</t>
+  </si>
+  <si>
+    <t>Lỗi Mã KH chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Lỗi Trùng Mã KH</t>
+  </si>
+  <si>
+    <t>Lỗi Email sai định dạng</t>
+  </si>
+  <si>
+    <t>Lỗi SĐT không bắt đầu bằng 0</t>
+  </si>
+  <si>
+    <t>Lỗi SĐT chứa chữ cái</t>
+  </si>
+  <si>
+    <t>Lỗi chưa đủ 18 tuổi</t>
+  </si>
+  <si>
+    <t>Lỗi chưa đồng ý điều khoản</t>
   </si>
 </sst>
 </file>
@@ -1443,22 +1440,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1010922</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>53618</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2417332</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>191364</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D79D3C0-55E2-8BD6-7BFA-96493D539DF3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5ECCA2A-DA0B-B20A-2607-6DB9D58FE394}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1474,8 +1471,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="409575" y="8829675"/>
-          <a:ext cx="9112887" cy="1991003"/>
+          <a:off x="0" y="8353425"/>
+          <a:ext cx="12841492" cy="6192114"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1492,22 +1489,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1542504</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>93862</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>521928</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>168753</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ECE4ED1-1888-2D11-43A0-CA6448D9738F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B4B1124-392D-6580-60F9-9FC14D61FD5D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1523,8 +1520,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="333375" y="9591675"/>
-          <a:ext cx="9734004" cy="3703837"/>
+          <a:off x="371475" y="9601200"/>
+          <a:ext cx="13342578" cy="7969728"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1816,13 +1813,13 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1847,7 +1844,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1895,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
@@ -1903,13 +1900,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1917,7 +1914,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1925,7 +1922,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1938,42 +1935,42 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
@@ -2004,13 +2001,13 @@
         <v>22</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="D25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" s="5">
         <v>120</v>
@@ -2027,13 +2024,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="D26" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E26" s="5">
         <v>1</v>
@@ -2050,19 +2047,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>23</v>
@@ -2073,13 +2070,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="E28" s="5">
         <v>30</v>
@@ -2096,13 +2093,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="E29" s="5">
         <v>2</v>
@@ -2139,13 +2136,13 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -2174,7 +2171,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2251,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -2261,14 +2258,14 @@
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -2278,14 +2275,14 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -2322,7 +2319,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -2333,7 +2330,7 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -2344,7 +2341,7 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2355,7 +2352,7 @@
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -2366,7 +2363,7 @@
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2377,7 +2374,7 @@
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2431,19 +2428,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>23</v>
@@ -2454,19 +2451,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>23</v>
@@ -2477,19 +2474,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>23</v>
@@ -2521,13 +2518,13 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -2556,7 +2553,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2633,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -2643,14 +2640,14 @@
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -2660,14 +2657,14 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -2680,7 +2677,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -2725,7 +2722,7 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2736,7 +2733,7 @@
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -2747,7 +2744,7 @@
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2758,7 +2755,7 @@
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2769,7 +2766,7 @@
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -2780,7 +2777,7 @@
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -2791,7 +2788,7 @@
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -2802,7 +2799,7 @@
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -2847,19 +2844,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>23</v>
@@ -2870,19 +2867,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>23</v>
@@ -2893,19 +2890,19 @@
         <v>25</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>23</v>
@@ -2916,19 +2913,19 @@
         <v>26</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>23</v>
@@ -2959,13 +2956,13 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -2994,7 +2991,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -3020,7 +3017,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>204</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -3071,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -3081,14 +3078,14 @@
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -3101,7 +3098,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -3114,7 +3111,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -3127,7 +3124,7 @@
         <v>5</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -3144,7 +3141,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -3155,7 +3152,7 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="6" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -3168,7 +3165,7 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="6" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3179,7 +3176,7 @@
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="6" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3190,7 +3187,7 @@
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="6" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -3201,7 +3198,7 @@
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="6" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3250,41 +3247,41 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>142</v>
-      </c>
       <c r="D23" s="5" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="E23" s="5">
         <v>50</v>
       </c>
       <c r="F23" s="5">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="E24" s="5">
         <v>100</v>
@@ -3296,41 +3293,41 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="E25" s="5">
         <v>80</v>
       </c>
       <c r="F25" s="5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="E26" s="5">
         <v>140</v>
@@ -3342,24 +3339,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>23</v>
@@ -3382,22 +3379,22 @@
     <col min="4" max="4" width="37.109375" style="7" customWidth="1"/>
     <col min="5" max="5" width="30.109375" style="7" customWidth="1"/>
     <col min="6" max="6" width="25.5546875" style="7" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="7" customWidth="1"/>
     <col min="8" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -3426,7 +3423,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -3452,7 +3449,7 @@
         <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -3496,14 +3493,14 @@
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -3513,14 +3510,14 @@
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -3530,14 +3527,14 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -3550,7 +3547,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -3576,7 +3573,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -3587,7 +3584,7 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="6" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -3598,7 +3595,7 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="6" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3609,7 +3606,7 @@
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="6" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3620,7 +3617,7 @@
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="6" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -3631,7 +3628,7 @@
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="6" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3685,19 +3682,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>23</v>
@@ -3708,19 +3705,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>23</v>
@@ -3731,19 +3728,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>23</v>
@@ -3754,19 +3751,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>23</v>
@@ -3777,19 +3774,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>23</v>
@@ -3800,19 +3797,19 @@
         <v>28</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>23</v>
@@ -3820,45 +3817,45 @@
     </row>
     <row r="29" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>23</v>
@@ -3866,45 +3863,45 @@
     </row>
     <row r="31" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>23</v>
